--- a/importer/tests/fixtures/gsa_frpp_sample.xlsx
+++ b/importer/tests/fixtures/gsa_frpp_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,35 +429,40 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Real Property Use</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Street Address</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>City Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>State Name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Zip Code</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Installation Name</t>
         </is>
@@ -476,31 +481,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>100 Main St</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>TEXAS</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>78701</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>30.2672</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>-97.7431</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Federal Office Building</t>
         </is>
@@ -519,25 +529,30 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Courthouse</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>200 Geocode Ave</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Houston</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>TEXAS</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>77002</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>US Courthouse Houston</t>
         </is>
@@ -556,31 +571,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>1 Bay St</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>CALIFORNIA</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>94105</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>37.79</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>-122.4</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>SF Federal Building</t>
         </is>
@@ -599,25 +619,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Vacant</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Rural Rd</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Marfa</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>TEXAS</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>79843</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Vacant Federal Land</t>
         </is>
@@ -634,24 +659,173 @@
           <t>Building</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Dallas</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>TEXAS</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>75201</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>No Address Building</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RPUID-TX-5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1 Bad Coord Rd</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Portland Mills</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TEXAS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>75001</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>43.0392538</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-87.9031992</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Mislocated Federal Building</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RPUID-TX-6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>500 Commerce St</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TEXAS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>75201</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>32.7767</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-96.797</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>DALLAS, TX</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RPUID-TX-7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Warehouses</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1234 Main Street</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TEXAS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>78704</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-97.75</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1234 Main Street</t>
         </is>
       </c>
     </row>
